--- a/survey_templates/044_technical_product_documentation_feedback_questionnaire--survey_templates.xlsx
+++ b/survey_templates/044_technical_product_documentation_feedback_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>welcome_to_the_feedback_questionnaire</t>
+          <t>Welcome to the Technical Product Documentation Feedback Questionnaire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_did_you_use_to_complete_this_questionnaire</t>
+          <t>What did you use to complete this questionnaire?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_did_you_like_about_the_questionnaire</t>
+          <t>What did you like most about the technical product documentation?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_did_you_dislike_about_the_questionnaire</t>
+          <t>What did you dislike about the technical product documentation?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_did_you_find_the_questionnaire</t>
+          <t>How did you find the technical product documentation?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_would_you_improve_about_the_questionnaire</t>
+          <t>What would you improve about the technical product documentation?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>do_you_have_any_other_comments</t>
+          <t>Do you have any other comments or suggestions?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Technical Product Documentation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>technical_product_documentation_feedback_questionnaire</t>
+          <t>Your Email Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Suggest a Different Title</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Suggest Changes to Content or Structure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>How Often Do You Use the Technical Product Documentation?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>What Do You Use the Technical Product Documentation for?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>How Easy Was It to Understand the Technical Product Documentation?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Suggest Additional Features or Tools</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>How Likely Are You to Recommend the Technical Product Documentation?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Technical Product Documentation Feedback</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,57 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>technical_product_documentation</t>
+          <t>Question 17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>technical_product_documentation</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>technical_product_documentation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1033,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1004,233 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>purpose_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Purpose 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>purpose_2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Purpose 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>purpose_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Purpose 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>very_easy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>somewhat_easy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Somewhat Easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>somewhat_difficult</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Somewhat Difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_difficult</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very Difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_15_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Very Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_15_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Somewhat Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_15_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
